--- a/analysis_sample2.xlsx
+++ b/analysis_sample2.xlsx
@@ -4672,7 +4672,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -4684,8 +4684,11 @@
       <b/>
       <color rgb="FFFFFFFF"/>
     </font>
+    <font>
+      <b/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -4695,6 +4698,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF6B6B"/>
       </patternFill>
     </fill>
     <fill>
@@ -4720,11 +4728,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5152,7 +5162,7 @@
       <c r="F2" t="s">
         <v>20</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="2" t="s">
         <v>22</v>
       </c>
       <c r="H2" t="s">
@@ -5193,7 +5203,7 @@
       <c r="A3" t="s">
         <v>29</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="2">
         <v>6</v>
       </c>
       <c r="C3" t="s">
@@ -5220,7 +5230,7 @@
       <c r="J3" t="s">
         <v>36</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="2">
         <v>0.49</v>
       </c>
       <c r="L3" t="s">
@@ -5249,7 +5259,7 @@
       <c r="A4" t="s">
         <v>39</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="2">
         <v>1</v>
       </c>
       <c r="C4" t="s">
@@ -5279,7 +5289,7 @@
       <c r="K4">
         <v>1</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="2" t="s">
         <v>45</v>
       </c>
       <c r="M4" t="s">
@@ -5294,7 +5304,7 @@
       <c r="P4">
         <v>1</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="2">
         <v>358</v>
       </c>
       <c r="R4">
@@ -5305,7 +5315,7 @@
       <c r="A5" t="s">
         <v>46</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="2">
         <v>6</v>
       </c>
       <c r="C5" t="s">
@@ -5335,7 +5345,7 @@
       <c r="K5">
         <v>0.31</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L5" s="2" t="s">
         <v>52</v>
       </c>
       <c r="M5" t="s">
@@ -5462,7 +5472,7 @@
       <c r="P7">
         <v>2.3</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" s="2">
         <v>207</v>
       </c>
       <c r="R7">
@@ -5473,7 +5483,7 @@
       <c r="A8" t="s">
         <v>73</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="2">
         <v>6</v>
       </c>
       <c r="C8" t="s">
@@ -5488,7 +5498,7 @@
       <c r="F8" t="s">
         <v>20</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="2" t="s">
         <v>74</v>
       </c>
       <c r="H8" t="s">
@@ -5500,7 +5510,7 @@
       <c r="J8" t="s">
         <v>76</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="2">
         <v>0.38</v>
       </c>
       <c r="L8" t="s">
@@ -5529,7 +5539,7 @@
       <c r="A9" t="s">
         <v>79</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="2">
         <v>2</v>
       </c>
       <c r="C9" t="s">
@@ -5574,7 +5584,7 @@
       <c r="P9">
         <v>1</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="2">
         <v>197</v>
       </c>
       <c r="R9">
@@ -5585,7 +5595,7 @@
       <c r="A10" t="s">
         <v>87</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="2">
         <v>2</v>
       </c>
       <c r="C10" t="s">
@@ -5600,7 +5610,7 @@
       <c r="F10" t="s">
         <v>20</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="2" t="s">
         <v>89</v>
       </c>
       <c r="H10" t="s">
@@ -5609,13 +5619,13 @@
       <c r="I10" t="s">
         <v>91</v>
       </c>
-      <c r="J10" t="s">
+      <c r="J10" s="2" t="s">
         <v>92</v>
       </c>
       <c r="K10">
         <v>0.53</v>
       </c>
-      <c r="L10" t="s">
+      <c r="L10" s="2" t="s">
         <v>93</v>
       </c>
       <c r="M10" t="s">
@@ -5633,7 +5643,7 @@
       <c r="Q10">
         <v>72</v>
       </c>
-      <c r="R10">
+      <c r="R10" s="3">
         <v>0.71</v>
       </c>
     </row>
@@ -5712,7 +5722,7 @@
       <c r="F12" t="s">
         <v>20</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" s="2" t="s">
         <v>107</v>
       </c>
       <c r="H12" t="s">
@@ -5721,10 +5731,10 @@
       <c r="I12" t="s">
         <v>109</v>
       </c>
-      <c r="J12" t="s">
+      <c r="J12" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="2">
         <v>0.48</v>
       </c>
       <c r="L12" t="s">
@@ -5895,7 +5905,7 @@
       <c r="K15">
         <v>0.29</v>
       </c>
-      <c r="L15" t="s">
+      <c r="L15" s="2" t="s">
         <v>135</v>
       </c>
       <c r="M15" t="s">
@@ -5921,7 +5931,7 @@
       <c r="A16" t="s">
         <v>137</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="2">
         <v>4</v>
       </c>
       <c r="C16" t="s">
@@ -5966,7 +5976,7 @@
       <c r="P16">
         <v>2</v>
       </c>
-      <c r="Q16">
+      <c r="Q16" s="2">
         <v>685</v>
       </c>
       <c r="R16">
@@ -6033,7 +6043,7 @@
       <c r="A18" t="s">
         <v>154</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="2">
         <v>3</v>
       </c>
       <c r="C18" t="s">
@@ -6048,7 +6058,7 @@
       <c r="F18" t="s">
         <v>20</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="2" t="s">
         <v>157</v>
       </c>
       <c r="H18" t="s">
@@ -6063,7 +6073,7 @@
       <c r="K18">
         <v>0.72</v>
       </c>
-      <c r="L18" t="s">
+      <c r="L18" s="2" t="s">
         <v>161</v>
       </c>
       <c r="M18" t="s">
@@ -6145,7 +6155,7 @@
       <c r="A20" t="s">
         <v>172</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="2">
         <v>6</v>
       </c>
       <c r="C20" t="s">
@@ -6160,7 +6170,7 @@
       <c r="F20" t="s">
         <v>20</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" s="2" t="s">
         <v>173</v>
       </c>
       <c r="H20" t="s">
@@ -6169,10 +6179,10 @@
       <c r="I20" t="s">
         <v>175</v>
       </c>
-      <c r="J20" t="s">
+      <c r="J20" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="2">
         <v>0.63</v>
       </c>
       <c r="L20" t="s">
@@ -6190,10 +6200,10 @@
       <c r="P20">
         <v>3</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" s="2">
         <v>455</v>
       </c>
-      <c r="R20">
+      <c r="R20" s="3">
         <v>0.74</v>
       </c>
     </row>
@@ -6455,7 +6465,7 @@
       <c r="K25">
         <v>0.22</v>
       </c>
-      <c r="L25" t="s">
+      <c r="L25" s="2" t="s">
         <v>225</v>
       </c>
       <c r="M25" t="s">
@@ -6481,7 +6491,7 @@
       <c r="A26" t="s">
         <v>227</v>
       </c>
-      <c r="B26">
+      <c r="B26" s="2">
         <v>4</v>
       </c>
       <c r="C26" t="s">
@@ -6537,7 +6547,7 @@
       <c r="A27" t="s">
         <v>235</v>
       </c>
-      <c r="B27">
+      <c r="B27" s="2">
         <v>5</v>
       </c>
       <c r="C27" t="s">
@@ -6552,7 +6562,7 @@
       <c r="F27" t="s">
         <v>20</v>
       </c>
-      <c r="G27" t="s">
+      <c r="G27" s="2" t="s">
         <v>238</v>
       </c>
       <c r="H27" t="s">
@@ -6561,7 +6571,7 @@
       <c r="I27" t="s">
         <v>240</v>
       </c>
-      <c r="J27" t="s">
+      <c r="J27" s="2" t="s">
         <v>241</v>
       </c>
       <c r="K27">
@@ -6664,7 +6674,7 @@
       <c r="F29" t="s">
         <v>20</v>
       </c>
-      <c r="G29" t="s">
+      <c r="G29" s="2" t="s">
         <v>255</v>
       </c>
       <c r="H29" t="s">
@@ -6673,7 +6683,7 @@
       <c r="I29" t="s">
         <v>257</v>
       </c>
-      <c r="J29" t="s">
+      <c r="J29" s="2" t="s">
         <v>258</v>
       </c>
       <c r="K29">
@@ -6788,10 +6798,10 @@
       <c r="J31" t="s">
         <v>276</v>
       </c>
-      <c r="K31">
+      <c r="K31" s="2">
         <v>0.75</v>
       </c>
-      <c r="L31" t="s">
+      <c r="L31" s="2" t="s">
         <v>277</v>
       </c>
       <c r="M31" t="s">
@@ -6806,10 +6816,10 @@
       <c r="P31">
         <v>10</v>
       </c>
-      <c r="Q31">
+      <c r="Q31" s="2">
         <v>1251</v>
       </c>
-      <c r="R31">
+      <c r="R31" s="3">
         <v>0.55</v>
       </c>
     </row>
@@ -6918,7 +6928,7 @@
       <c r="P33">
         <v>2.8</v>
       </c>
-      <c r="Q33">
+      <c r="Q33" s="2">
         <v>193</v>
       </c>
       <c r="R33">
@@ -6953,7 +6963,7 @@
       <c r="I34" t="s">
         <v>302</v>
       </c>
-      <c r="J34" t="s">
+      <c r="J34" s="2" t="s">
         <v>303</v>
       </c>
       <c r="K34">
@@ -7000,7 +7010,7 @@
       <c r="F35" t="s">
         <v>20</v>
       </c>
-      <c r="G35" t="s">
+      <c r="G35" s="2" t="s">
         <v>307</v>
       </c>
       <c r="H35" t="s">
@@ -7009,7 +7019,7 @@
       <c r="I35" t="s">
         <v>309</v>
       </c>
-      <c r="J35" t="s">
+      <c r="J35" s="2" t="s">
         <v>310</v>
       </c>
       <c r="K35">
@@ -7041,7 +7051,7 @@
       <c r="A36" t="s">
         <v>313</v>
       </c>
-      <c r="B36">
+      <c r="B36" s="2">
         <v>3</v>
       </c>
       <c r="C36" t="s">
@@ -7124,7 +7134,7 @@
       <c r="J37" t="s">
         <v>324</v>
       </c>
-      <c r="K37">
+      <c r="K37" s="2">
         <v>0.4</v>
       </c>
       <c r="L37" t="s">
@@ -7142,7 +7152,7 @@
       <c r="P37">
         <v>2.7</v>
       </c>
-      <c r="Q37">
+      <c r="Q37" s="2">
         <v>289</v>
       </c>
       <c r="R37">
@@ -7183,7 +7193,7 @@
       <c r="K38">
         <v>0.25</v>
       </c>
-      <c r="L38" t="s">
+      <c r="L38" s="2" t="s">
         <v>332</v>
       </c>
       <c r="M38" t="s">
@@ -7198,7 +7208,7 @@
       <c r="P38">
         <v>7</v>
       </c>
-      <c r="Q38">
+      <c r="Q38" s="2">
         <v>217</v>
       </c>
       <c r="R38">
@@ -7236,7 +7246,7 @@
       <c r="J39" t="s">
         <v>338</v>
       </c>
-      <c r="K39">
+      <c r="K39" s="2">
         <v>0.41</v>
       </c>
       <c r="L39" t="s">
@@ -7289,7 +7299,7 @@
       <c r="I40" t="s">
         <v>345</v>
       </c>
-      <c r="J40" t="s">
+      <c r="J40" s="2" t="s">
         <v>346</v>
       </c>
       <c r="K40">
@@ -7310,7 +7320,7 @@
       <c r="P40">
         <v>2.3</v>
       </c>
-      <c r="Q40">
+      <c r="Q40" s="2">
         <v>162</v>
       </c>
       <c r="R40">
@@ -7321,7 +7331,7 @@
       <c r="A41" t="s">
         <v>349</v>
       </c>
-      <c r="B41">
+      <c r="B41" s="2">
         <v>6</v>
       </c>
       <c r="C41" t="s">
@@ -7351,7 +7361,7 @@
       <c r="K41">
         <v>0.37</v>
       </c>
-      <c r="L41" t="s">
+      <c r="L41" s="2" t="s">
         <v>355</v>
       </c>
       <c r="M41" t="s">
@@ -7433,7 +7443,7 @@
       <c r="A43" t="s">
         <v>364</v>
       </c>
-      <c r="B43">
+      <c r="B43" s="2">
         <v>4</v>
       </c>
       <c r="C43" t="s">
@@ -7448,7 +7458,7 @@
       <c r="F43" t="s">
         <v>20</v>
       </c>
-      <c r="G43" t="s">
+      <c r="G43" s="2" t="s">
         <v>366</v>
       </c>
       <c r="H43" t="s">
@@ -7457,13 +7467,13 @@
       <c r="I43" t="s">
         <v>368</v>
       </c>
-      <c r="J43" t="s">
+      <c r="J43" s="2" t="s">
         <v>369</v>
       </c>
       <c r="K43">
         <v>0.56</v>
       </c>
-      <c r="L43" t="s">
+      <c r="L43" s="2" t="s">
         <v>370</v>
       </c>
       <c r="M43" t="s">
@@ -7481,7 +7491,7 @@
       <c r="Q43">
         <v>79</v>
       </c>
-      <c r="R43">
+      <c r="R43" s="3">
         <v>0.71</v>
       </c>
     </row>
@@ -7489,7 +7499,7 @@
       <c r="A44" t="s">
         <v>372</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="2">
         <v>5</v>
       </c>
       <c r="C44" t="s">
@@ -7560,7 +7570,7 @@
       <c r="F45" t="s">
         <v>20</v>
       </c>
-      <c r="G45" t="s">
+      <c r="G45" s="2" t="s">
         <v>382</v>
       </c>
       <c r="H45" t="s">
@@ -7569,10 +7579,10 @@
       <c r="I45" t="s">
         <v>384</v>
       </c>
-      <c r="J45" t="s">
+      <c r="J45" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="K45">
+      <c r="K45" s="2">
         <v>0.5</v>
       </c>
       <c r="L45" t="s">
@@ -7601,7 +7611,7 @@
       <c r="A46" t="s">
         <v>388</v>
       </c>
-      <c r="B46">
+      <c r="B46" s="2">
         <v>3</v>
       </c>
       <c r="C46" t="s">
@@ -7631,7 +7641,7 @@
       <c r="K46">
         <v>0.78</v>
       </c>
-      <c r="L46" t="s">
+      <c r="L46" s="2" t="s">
         <v>393</v>
       </c>
       <c r="M46" t="s">
@@ -7646,7 +7656,7 @@
       <c r="P46">
         <v>3</v>
       </c>
-      <c r="Q46">
+      <c r="Q46" s="2">
         <v>2697</v>
       </c>
       <c r="R46">
@@ -7657,7 +7667,7 @@
       <c r="A47" t="s">
         <v>395</v>
       </c>
-      <c r="B47">
+      <c r="B47" s="2">
         <v>6</v>
       </c>
       <c r="C47" t="s">
@@ -7672,7 +7682,7 @@
       <c r="F47" t="s">
         <v>20</v>
       </c>
-      <c r="G47" t="s">
+      <c r="G47" s="2" t="s">
         <v>396</v>
       </c>
       <c r="H47" t="s">
@@ -7681,13 +7691,13 @@
       <c r="I47" t="s">
         <v>398</v>
       </c>
-      <c r="J47" t="s">
+      <c r="J47" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="K47">
+      <c r="K47" s="2">
         <v>0.38</v>
       </c>
-      <c r="L47" t="s">
+      <c r="L47" s="2" t="s">
         <v>400</v>
       </c>
       <c r="M47" t="s">
@@ -7702,10 +7712,10 @@
       <c r="P47">
         <v>6</v>
       </c>
-      <c r="Q47">
+      <c r="Q47" s="2">
         <v>183</v>
       </c>
-      <c r="R47">
+      <c r="R47" s="3">
         <v>1</v>
       </c>
     </row>
@@ -7728,7 +7738,7 @@
       <c r="F48" t="s">
         <v>20</v>
       </c>
-      <c r="G48" t="s">
+      <c r="G48" s="2" t="s">
         <v>403</v>
       </c>
       <c r="H48" t="s">
@@ -7743,7 +7753,7 @@
       <c r="K48">
         <v>0.3</v>
       </c>
-      <c r="L48" t="s">
+      <c r="L48" s="2" t="s">
         <v>407</v>
       </c>
       <c r="M48" t="s">
@@ -7758,10 +7768,10 @@
       <c r="P48">
         <v>7</v>
       </c>
-      <c r="Q48">
+      <c r="Q48" s="2">
         <v>200</v>
       </c>
-      <c r="R48">
+      <c r="R48" s="3">
         <v>0.56</v>
       </c>
     </row>
@@ -7769,7 +7779,7 @@
       <c r="A49" t="s">
         <v>409</v>
       </c>
-      <c r="B49">
+      <c r="B49" s="2">
         <v>6</v>
       </c>
       <c r="C49" t="s">
@@ -7796,10 +7806,10 @@
       <c r="J49" t="s">
         <v>413</v>
       </c>
-      <c r="K49">
+      <c r="K49" s="2">
         <v>0.56</v>
       </c>
-      <c r="L49" t="s">
+      <c r="L49" s="2" t="s">
         <v>414</v>
       </c>
       <c r="M49" t="s">
@@ -7814,10 +7824,10 @@
       <c r="P49">
         <v>6</v>
       </c>
-      <c r="Q49">
+      <c r="Q49" s="2">
         <v>254</v>
       </c>
-      <c r="R49">
+      <c r="R49" s="3">
         <v>0.73</v>
       </c>
     </row>
@@ -7825,7 +7835,7 @@
       <c r="A50" t="s">
         <v>416</v>
       </c>
-      <c r="B50">
+      <c r="B50" s="2">
         <v>3</v>
       </c>
       <c r="C50" t="s">
@@ -7855,7 +7865,7 @@
       <c r="K50">
         <v>0.5</v>
       </c>
-      <c r="L50" t="s">
+      <c r="L50" s="2" t="s">
         <v>420</v>
       </c>
       <c r="M50" t="s">
@@ -7870,7 +7880,7 @@
       <c r="P50">
         <v>3</v>
       </c>
-      <c r="Q50">
+      <c r="Q50" s="2">
         <v>2753</v>
       </c>
       <c r="R50">
@@ -7908,7 +7918,7 @@
       <c r="J51" t="s">
         <v>426</v>
       </c>
-      <c r="K51">
+      <c r="K51" s="2">
         <v>0.49</v>
       </c>
       <c r="L51" t="s">
@@ -7953,26 +7963,26 @@
     <col min="7" max="7" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="4" t="s">
         <v>429</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>430</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>432</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="4" t="s">
         <v>433</v>
       </c>
     </row>
@@ -11955,65 +11965,65 @@
     <col min="17" max="20" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
         <v>429</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="5" t="s">
         <v>436</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="C1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>437</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="5" t="s">
         <v>438</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>439</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="5" t="s">
         <v>440</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="5" t="s">
         <v>441</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="5" t="s">
         <v>442</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="5" t="s">
         <v>443</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="5" t="s">
         <v>444</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="5" t="s">
         <v>445</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="5" t="s">
         <v>446</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="5" t="s">
         <v>447</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="5" t="s">
         <v>448</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="5" t="s">
         <v>449</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="5" t="s">
         <v>451</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="S1" s="5" t="s">
         <v>452</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="T1" s="5" t="s">
         <v>433</v>
       </c>
     </row>

--- a/analysis_sample2.xlsx
+++ b/analysis_sample2.xlsx
@@ -63,7 +63,7 @@
     <t>Avg Commits</t>
   </si>
   <si>
-    <t>Avg Changes/h</t>
+    <t>Avg Changes/h over session</t>
   </si>
   <si>
     <t>Index</t>
